--- a/AtchisonRegime/Outputs/UK/MSCI_UK 100/df_regSummary_MSCI_UK 100.xlsx
+++ b/AtchisonRegime/Outputs/UK/MSCI_UK 100/df_regSummary_MSCI_UK 100.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G2" t="n">
-        <v>0.594594363170928</v>
+        <v>0.5685092704662653</v>
       </c>
       <c r="H2" t="n">
-        <v>3.68975023032526</v>
+        <v>3.680602917018617</v>
       </c>
       <c r="I2" t="n">
         <v>-13.62015137901101</v>
@@ -545,16 +545,16 @@
         <v>8.857295173845369</v>
       </c>
       <c r="K2" t="n">
-        <v>29.41176470588236</v>
+        <v>29.61876832844575</v>
       </c>
       <c r="L2" t="n">
         <v>13</v>
       </c>
       <c r="M2" t="n">
-        <v>7.692307692307693</v>
+        <v>7.769230769230769</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04813473394775439</v>
+        <v>0.04659751548621593</v>
       </c>
       <c r="O2" t="n">
         <v>-0.2007476969399158</v>
@@ -603,7 +603,7 @@
         <v>8.088606111855423</v>
       </c>
       <c r="K3" t="n">
-        <v>18.82352941176471</v>
+        <v>18.7683284457478</v>
       </c>
       <c r="L3" t="n">
         <v>10</v>
@@ -661,7 +661,7 @@
         <v>12.69</v>
       </c>
       <c r="K4" t="n">
-        <v>28.23529411764706</v>
+        <v>28.1524926686217</v>
       </c>
       <c r="L4" t="n">
         <v>12</v>
@@ -719,7 +719,7 @@
         <v>8.654138875819871</v>
       </c>
       <c r="K5" t="n">
-        <v>23.52941176470588</v>
+        <v>23.46041055718475</v>
       </c>
       <c r="L5" t="n">
         <v>8</v>
